--- a/docs/downloads/05/tbl_water_alaotra_avaradrano.xlsx
+++ b/docs/downloads/05/tbl_water_alaotra_avaradrano.xlsx
@@ -405,12 +405,6 @@
           <t>Cours d?eau</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -418,12 +412,6 @@
           <t>Alaotra - Avaradrano</t>
         </is>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -556,12 +544,6 @@
         <is>
           <t>Alaotra - Tous</t>
         </is>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>0.2</v>
       </c>
     </row>
   </sheetData>
